--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F315E8-C2CE-4B8E-A5E8-72AC4C31F49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB4D6DB-CDA2-4E58-8ADC-36D7F86B9E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2110,7 +2110,7 @@
         <v>30</v>
       </c>
       <c r="D29" s="14">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E29" s="14">
         <v>30</v>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB4D6DB-CDA2-4E58-8ADC-36D7F86B9E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCD8A7-1EF3-4318-BB8E-91E12580266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2141,31 +2141,55 @@
       <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="17"/>
+      <c r="N29" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46289</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>240</v>
+      </c>
+      <c r="E30" s="14">
+        <v>10</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCD8A7-1EF3-4318-BB8E-91E12580266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF2C677-7309-4AC9-ACB5-DFE17A3E98EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>Holiday full of fun and no stress at all</t>
   </si>
   <si>
     <t>Tired  and too much classes.</t>
@@ -1961,7 +1958,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>46285</v>
       </c>
@@ -2004,7 +2001,7 @@
         <v>62</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2096,7 +2093,7 @@
         <v>59</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2195,20 +2192,24 @@
       <c r="A31" s="13">
         <v>46290</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="14">
+        <v>380</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1040</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
@@ -10384,6 +10385,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF2C677-7309-4AC9-ACB5-DFE17A3E98EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E8E893-79D6-4C52-B726-6346D27A8054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,6 +261,12 @@
   <si>
     <t>Tired  and too much classes.</t>
   </si>
+  <si>
+    <t>Day was positive.</t>
+  </si>
+  <si>
+    <t>Well spent day.</t>
+  </si>
 </sst>
 </file>
 
@@ -371,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -394,11 +400,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -439,9 +491,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -910,7 +964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N417"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -925,36 +979,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="19">
         <v>12602993</v>
       </c>
       <c r="G2" s="20"/>
@@ -963,36 +1017,36 @@
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="19" t="s">
         <v>56</v>
       </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1064,11 +1118,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I85" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J85" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1084,176 +1138,176 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46266</v>
+        <v>46250</v>
       </c>
       <c r="B7" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C7" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D7" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E7" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F7" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>1070</v>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>450</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>990</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46267</v>
+        <v>46251</v>
       </c>
       <c r="B8" s="14">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="C8" s="14">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14">
         <v>30</v>
       </c>
-      <c r="D8" s="14">
-        <v>80</v>
-      </c>
       <c r="E8" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G8" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="14">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f t="shared" ref="I8:I71" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>795</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>645</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46268</v>
+        <v>46252</v>
       </c>
       <c r="B9" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C9" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D9" s="14">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E9" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" s="14">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G9" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>870</v>
+        <f t="shared" si="2"/>
+        <v>890</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46269</v>
+        <v>46253</v>
       </c>
       <c r="B10" s="14">
-        <v>540</v>
+        <v>380</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D10" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E10" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F10" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G10" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="14">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>1010</v>
+        <f t="shared" si="2"/>
+        <v>755</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>685</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1262,136 +1316,136 @@
         <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46270</v>
+        <v>46254</v>
       </c>
       <c r="B11" s="14">
-        <v>560</v>
+        <v>360</v>
       </c>
       <c r="C11" s="14">
         <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E11" s="14">
         <v>0</v>
       </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="14">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>680</v>
+        <f t="shared" si="2"/>
+        <v>710</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>730</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46271</v>
+        <v>46255</v>
       </c>
       <c r="B12" s="14">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="C12" s="14">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E12" s="14">
         <v>0</v>
       </c>
       <c r="F12" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G12" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="14">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>810</v>
+        <f t="shared" si="2"/>
+        <v>780</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>630</v>
+        <f>IF(I12="","",1440-I12)</f>
+        <v>660</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46272</v>
+        <v>46256</v>
       </c>
       <c r="B13" s="14">
-        <v>460</v>
+        <v>540</v>
       </c>
       <c r="C13" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D13" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E13" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F13" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>970</v>
+        <f t="shared" si="2"/>
+        <v>540</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>900</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1408,39 +1462,39 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46273</v>
+        <v>46257</v>
       </c>
       <c r="B14" s="14">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="C14" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D14" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E14" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>1010</v>
+        <f t="shared" si="2"/>
+        <v>555</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>885</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>57</v>
@@ -1449,363 +1503,363 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46274</v>
+        <v>46258</v>
       </c>
       <c r="B15" s="14">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>80</v>
+      </c>
+      <c r="E15" s="14">
+        <v>10</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
         <v>30</v>
       </c>
-      <c r="D15" s="14">
-        <v>200</v>
-      </c>
-      <c r="E15" s="14">
-        <v>40</v>
-      </c>
-      <c r="F15" s="14">
-        <v>300</v>
-      </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
-      <c r="H15" s="14">
-        <v>80</v>
-      </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>1130</v>
+        <f t="shared" si="2"/>
+        <v>770</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>670</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="B16" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E16" s="14">
         <v>30</v>
       </c>
       <c r="F16" s="14">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>830</v>
+        <f t="shared" si="2"/>
+        <v>820</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46276</v>
+        <v>46260</v>
       </c>
       <c r="B17" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E17" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F17" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>980</v>
+        <f t="shared" si="2"/>
+        <v>860</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46277</v>
+        <v>46261</v>
       </c>
       <c r="B18" s="14">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C18" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G18" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>770</v>
+        <f t="shared" si="2"/>
+        <v>920</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>520</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46278</v>
+        <v>46262</v>
       </c>
       <c r="B19" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="C19" s="14">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F19" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G19" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="14">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>620</v>
+        <f t="shared" si="2"/>
+        <v>610</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="M19" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46279</v>
+        <v>46263</v>
       </c>
       <c r="B20" s="14">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="C20" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D20" s="14">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E20" s="14">
         <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>950</v>
+        <f t="shared" si="2"/>
+        <v>635</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>805</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46280</v>
+        <v>46264</v>
       </c>
       <c r="B21" s="14">
-        <v>380</v>
+        <v>600</v>
       </c>
       <c r="C21" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D21" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F21" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>925</v>
+        <f t="shared" si="2"/>
+        <v>620</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>515</v>
+        <v>820</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="B22" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C22" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D22" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E22" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f t="shared" si="2"/>
+        <v>830</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>610</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1817,87 +1871,87 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46282</v>
+        <v>46266</v>
       </c>
       <c r="B23" s="14">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C23" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D23" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E23" s="14">
         <v>30</v>
       </c>
       <c r="F23" s="14">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <f t="shared" si="2"/>
+        <v>1040</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>400</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46283</v>
+        <v>46267</v>
       </c>
       <c r="B24" s="14">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E24" s="14">
         <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
-        <v>890</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>440</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1906,99 +1960,99 @@
         <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46284</v>
+        <v>46268</v>
       </c>
       <c r="B25" s="14">
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="C25" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G25" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" s="14">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
-        <v>640</v>
+        <f t="shared" si="2"/>
+        <v>835</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>605</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46285</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="14">
-        <v>680</v>
+        <v>540</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F26" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G26" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" s="14">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
-        <v>1210</v>
+        <f t="shared" si="2"/>
+        <v>955</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>485</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
         <v>67</v>
@@ -2006,567 +2060,969 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46286</v>
+        <v>46270</v>
       </c>
       <c r="B27" s="14">
-        <v>420</v>
+        <v>560</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
       </c>
       <c r="D27" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E27" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="14">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="0"/>
-        <v>940</v>
+        <f t="shared" si="2"/>
+        <v>640</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46287</v>
+        <v>46271</v>
       </c>
       <c r="B28" s="14">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="C28" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D28" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E28" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>1130</v>
+        <f t="shared" si="2"/>
+        <v>720</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>720</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46288</v>
+        <v>46272</v>
       </c>
       <c r="B29" s="14">
-        <v>340</v>
+        <v>460</v>
       </c>
       <c r="C29" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="E29" s="14">
         <v>30</v>
       </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>940</v>
+        <f t="shared" si="2"/>
+        <v>900</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46289</v>
+        <v>46273</v>
       </c>
       <c r="B30" s="14">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C30" s="14">
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="E30" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30" s="14">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H30" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <f t="shared" si="2"/>
+        <v>890</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46290</v>
+        <v>46274</v>
       </c>
       <c r="B31" s="14">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="C31" s="14">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="14">
+        <v>80</v>
+      </c>
       <c r="I31" s="15">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="2"/>
+        <v>1130</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>310</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>90</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B33" s="14">
+        <v>440</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="2"/>
+        <v>920</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>150</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>40</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="14">
+        <v>450</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="2"/>
+        <v>610</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>830</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>20</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" si="2"/>
+        <v>890</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B37" s="14">
+        <v>380</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>15</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>20</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="2"/>
+        <v>855</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B38" s="14">
+        <v>400</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>80</v>
+      </c>
+      <c r="E38" s="14">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14">
+        <v>30</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="14">
+        <v>450</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>50</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>150</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>20</v>
+      </c>
+      <c r="D40" s="14">
+        <v>60</v>
+      </c>
+      <c r="E40" s="14">
+        <v>20</v>
+      </c>
+      <c r="F40" s="14">
+        <v>250</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>45</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="2"/>
+        <v>815</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B41" s="14">
+        <v>350</v>
+      </c>
+      <c r="C41" s="14">
+        <v>40</v>
+      </c>
+      <c r="D41" s="14">
+        <v>0</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>50</v>
+      </c>
+      <c r="G41" s="14">
+        <v>1</v>
+      </c>
+      <c r="H41" s="14">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" si="2"/>
+        <v>620</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="14">
+        <v>680</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="2"/>
+        <v>1120</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>250</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>45</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="2"/>
+        <v>895</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>545</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>350</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>90</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="2"/>
+        <v>1100</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B45" s="14">
+        <v>340</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>160</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14">
+        <v>50</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="2"/>
+        <v>910</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>10</v>
+      </c>
+      <c r="F46" s="14">
+        <v>150</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>60</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>20</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>80</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" si="2"/>
+        <v>970</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
@@ -2578,7 +3034,7 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J48" s="15" t="str">
@@ -2600,7 +3056,7 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
@@ -2622,7 +3078,7 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
@@ -2644,7 +3100,7 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
@@ -2666,7 +3122,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
@@ -2688,7 +3144,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
@@ -2710,7 +3166,7 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
@@ -2732,7 +3188,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
@@ -2754,7 +3210,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
@@ -2776,7 +3232,7 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
@@ -2798,7 +3254,7 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
@@ -2820,7 +3276,7 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
@@ -2842,7 +3298,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
@@ -2864,7 +3320,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
@@ -2886,7 +3342,7 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
@@ -2908,7 +3364,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
@@ -2930,7 +3386,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
@@ -2952,7 +3408,7 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
@@ -2974,7 +3430,7 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
@@ -2996,7 +3452,7 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
@@ -3018,7 +3474,7 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
@@ -3040,7 +3496,7 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
@@ -3062,11 +3518,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3088,7 +3544,7 @@
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3106,11 +3562,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I72:I100" si="3">IF(SUM(B72:F72,H72)=0,"",SUM(B72:F72,H72))</f>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3128,11 +3584,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3150,11 +3606,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3172,11 +3628,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3194,11 +3650,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3216,11 +3672,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3238,11 +3694,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3260,11 +3716,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3282,11 +3738,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3304,11 +3760,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3326,11 +3782,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3348,11 +3804,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3370,11 +3826,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3392,11 +3848,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3414,11 +3870,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J86:J149" si="4">IF(I86="","",1440-I86)</f>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3436,11 +3892,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3458,11 +3914,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3480,11 +3936,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3502,11 +3958,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3524,11 +3980,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3546,11 +4002,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3568,11 +4024,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3590,11 +4046,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3612,11 +4068,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3634,11 +4090,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3656,11 +4112,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3678,11 +4134,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3700,11 +4156,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3722,11 +4178,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3744,11 +4200,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I86:I149" si="5">IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3766,11 +4222,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3788,11 +4244,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3810,11 +4266,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3832,11 +4288,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3854,11 +4310,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3876,11 +4332,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3898,11 +4354,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3920,11 +4376,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3942,11 +4398,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3964,11 +4420,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3986,11 +4442,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4008,11 +4464,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4030,11 +4486,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4052,11 +4508,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4074,11 +4530,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4096,11 +4552,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4118,11 +4574,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4140,11 +4596,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4162,11 +4618,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4184,11 +4640,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4206,11 +4662,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4228,11 +4684,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4250,11 +4706,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4272,11 +4728,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4294,11 +4750,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4316,11 +4772,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4338,11 +4794,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4360,11 +4816,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4382,11 +4838,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4404,11 +4860,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4426,11 +4882,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4448,11 +4904,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4470,11 +4926,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4492,11 +4948,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J135" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4514,11 +4970,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J136" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4536,11 +4992,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J137" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4558,11 +5014,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J138" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4580,11 +5036,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J139" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4602,11 +5058,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J140" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4624,11 +5080,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J141" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4646,11 +5102,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J142" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4668,11 +5124,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J143" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4690,11 +5146,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J144" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4712,11 +5168,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J145" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4734,11 +5190,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J146" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4756,11 +5212,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J147" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4778,11 +5234,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J148" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4800,11 +5256,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J149" s="15" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4822,11 +5278,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I150:I213" si="6">IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J150:J213" si="7">IF(I150="","",1440-I150)</f>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4844,11 +5300,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4866,11 +5322,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4888,11 +5344,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4910,11 +5366,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4932,11 +5388,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4954,11 +5410,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4976,11 +5432,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4998,11 +5454,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5020,11 +5476,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5042,11 +5498,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5064,11 +5520,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5086,11 +5542,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5108,11 +5564,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5130,11 +5586,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5152,11 +5608,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5174,11 +5630,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5196,11 +5652,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5218,11 +5674,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5240,11 +5696,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5262,11 +5718,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5284,11 +5740,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5306,11 +5762,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5328,11 +5784,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5350,11 +5806,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5372,11 +5828,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5394,11 +5850,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5416,11 +5872,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5438,11 +5894,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5460,11 +5916,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5482,11 +5938,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5504,11 +5960,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5526,11 +5982,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5548,11 +6004,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5570,11 +6026,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5592,11 +6048,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5614,11 +6070,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5636,11 +6092,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5658,11 +6114,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5680,11 +6136,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5702,11 +6158,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5724,11 +6180,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5746,11 +6202,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5768,11 +6224,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5790,11 +6246,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5812,11 +6268,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5834,11 +6290,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5856,11 +6312,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5878,11 +6334,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6230,11 +6686,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I214:I277" si="8">IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J214:J277" si="9">IF(I214="","",1440-I214)</f>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6252,11 +6708,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6274,11 +6730,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6296,11 +6752,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6318,11 +6774,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6340,11 +6796,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6362,11 +6818,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6384,11 +6840,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6406,11 +6862,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6428,11 +6884,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6450,11 +6906,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6472,11 +6928,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6494,11 +6950,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6516,11 +6972,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6538,11 +6994,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6560,11 +7016,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6582,11 +7038,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6604,11 +7060,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6626,11 +7082,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6648,11 +7104,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6670,11 +7126,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6692,11 +7148,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6714,11 +7170,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6736,11 +7192,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6758,11 +7214,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6780,11 +7236,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6802,11 +7258,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6824,11 +7280,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6846,11 +7302,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6868,11 +7324,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6890,11 +7346,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6912,11 +7368,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6934,11 +7390,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6956,11 +7412,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6978,11 +7434,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7000,11 +7456,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7022,11 +7478,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7044,11 +7500,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7066,11 +7522,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7088,11 +7544,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7110,11 +7566,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7132,11 +7588,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7154,11 +7610,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7176,11 +7632,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7198,11 +7654,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7220,11 +7676,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7242,11 +7698,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7264,11 +7720,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7286,11 +7742,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7638,11 +8094,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I278:I341" si="10">IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J278:J341" si="11">IF(I278="","",1440-I278)</f>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7660,11 +8116,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7682,11 +8138,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7704,11 +8160,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7726,11 +8182,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7748,11 +8204,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7770,11 +8226,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7792,11 +8248,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7814,11 +8270,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7836,11 +8292,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7858,11 +8314,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7880,11 +8336,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7902,11 +8358,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7924,11 +8380,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7946,11 +8402,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7968,11 +8424,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7990,11 +8446,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8012,11 +8468,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8034,11 +8490,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8056,11 +8512,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8078,11 +8534,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8100,11 +8556,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8122,11 +8578,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8144,11 +8600,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8166,11 +8622,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8188,11 +8644,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8210,11 +8666,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8232,11 +8688,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8254,11 +8710,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8276,11 +8732,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8298,11 +8754,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8320,11 +8776,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8342,11 +8798,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8364,11 +8820,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8386,11 +8842,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8408,11 +8864,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8430,11 +8886,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8452,11 +8908,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8474,11 +8930,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8496,11 +8952,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8518,11 +8974,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8540,11 +8996,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8562,11 +9018,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8584,11 +9040,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8606,11 +9062,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8628,11 +9084,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8650,11 +9106,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8672,11 +9128,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8694,11 +9150,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9046,11 +9502,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I342:I405" si="12">IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J342:J405" si="13">IF(I342="","",1440-I342)</f>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9068,11 +9524,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9090,11 +9546,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9112,11 +9568,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9134,11 +9590,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9156,11 +9612,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9178,11 +9634,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9200,11 +9656,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9222,11 +9678,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9244,11 +9700,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9266,11 +9722,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9288,11 +9744,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9310,11 +9766,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9332,11 +9788,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9354,11 +9810,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9376,11 +9832,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9398,11 +9854,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9420,11 +9876,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9442,11 +9898,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9464,11 +9920,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9486,11 +9942,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9508,11 +9964,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9530,11 +9986,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9552,11 +10008,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9574,11 +10030,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9596,11 +10052,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9618,11 +10074,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9640,11 +10096,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9662,11 +10118,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9684,11 +10140,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9706,11 +10162,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9728,11 +10184,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9750,11 +10206,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9772,11 +10228,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9794,11 +10250,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9816,11 +10272,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9838,11 +10294,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9860,11 +10316,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9882,11 +10338,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9904,11 +10360,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9926,11 +10382,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9948,11 +10404,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9970,11 +10426,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9992,11 +10448,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10014,11 +10470,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10036,11 +10492,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10058,11 +10514,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10080,11 +10536,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10102,11 +10558,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10356,6 +10812,358 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A406" s="13"/>
+      <c r="B406" s="14"/>
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="15" t="str">
+        <f t="shared" ref="I406:I417" si="14">IF(SUM(B406:F406,H406)=0,"",SUM(B406:F406,H406))</f>
+        <v/>
+      </c>
+      <c r="J406" s="15" t="str">
+        <f t="shared" ref="J406:J417" si="15">IF(I406="","",1440-I406)</f>
+        <v/>
+      </c>
+      <c r="K406" s="16"/>
+      <c r="L406" s="16"/>
+      <c r="M406" s="16"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A407" s="13"/>
+      <c r="B407" s="14"/>
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J407" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K407" s="16"/>
+      <c r="L407" s="16"/>
+      <c r="M407" s="16"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A408" s="13"/>
+      <c r="B408" s="14"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J408" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K408" s="16"/>
+      <c r="L408" s="16"/>
+      <c r="M408" s="16"/>
+      <c r="N408" s="17"/>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A409" s="13"/>
+      <c r="B409" s="14"/>
+      <c r="C409" s="14"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="14"/>
+      <c r="F409" s="14"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="I409" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J409" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K409" s="16"/>
+      <c r="L409" s="16"/>
+      <c r="M409" s="16"/>
+      <c r="N409" s="17"/>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A410" s="13"/>
+      <c r="B410" s="14"/>
+      <c r="C410" s="14"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="14"/>
+      <c r="F410" s="14"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="I410" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J410" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K410" s="16"/>
+      <c r="L410" s="16"/>
+      <c r="M410" s="16"/>
+      <c r="N410" s="17"/>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A411" s="13"/>
+      <c r="B411" s="14"/>
+      <c r="C411" s="14"/>
+      <c r="D411" s="14"/>
+      <c r="E411" s="14"/>
+      <c r="F411" s="14"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="I411" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J411" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K411" s="16"/>
+      <c r="L411" s="16"/>
+      <c r="M411" s="16"/>
+      <c r="N411" s="17"/>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A412" s="13"/>
+      <c r="B412" s="14"/>
+      <c r="C412" s="14"/>
+      <c r="D412" s="14"/>
+      <c r="E412" s="14"/>
+      <c r="F412" s="14"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="I412" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J412" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K412" s="16"/>
+      <c r="L412" s="16"/>
+      <c r="M412" s="16"/>
+      <c r="N412" s="17"/>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A413" s="13"/>
+      <c r="B413" s="14"/>
+      <c r="C413" s="14"/>
+      <c r="D413" s="14"/>
+      <c r="E413" s="14"/>
+      <c r="F413" s="14"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="I413" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J413" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K413" s="16"/>
+      <c r="L413" s="16"/>
+      <c r="M413" s="16"/>
+      <c r="N413" s="17"/>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A414" s="13"/>
+      <c r="B414" s="14"/>
+      <c r="C414" s="14"/>
+      <c r="D414" s="14"/>
+      <c r="E414" s="14"/>
+      <c r="F414" s="14"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="I414" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J414" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K414" s="16"/>
+      <c r="L414" s="16"/>
+      <c r="M414" s="16"/>
+      <c r="N414" s="17"/>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A415" s="13"/>
+      <c r="B415" s="14"/>
+      <c r="C415" s="14"/>
+      <c r="D415" s="14"/>
+      <c r="E415" s="14"/>
+      <c r="F415" s="14"/>
+      <c r="G415" s="14"/>
+      <c r="H415" s="14"/>
+      <c r="I415" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J415" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K415" s="16"/>
+      <c r="L415" s="16"/>
+      <c r="M415" s="16"/>
+      <c r="N415" s="17"/>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A416" s="13"/>
+      <c r="B416" s="14"/>
+      <c r="C416" s="14"/>
+      <c r="D416" s="14"/>
+      <c r="E416" s="14"/>
+      <c r="F416" s="14"/>
+      <c r="G416" s="14"/>
+      <c r="H416" s="14"/>
+      <c r="I416" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J416" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K416" s="16"/>
+      <c r="L416" s="16"/>
+      <c r="M416" s="16"/>
+      <c r="N416" s="17"/>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A417" s="13"/>
+      <c r="B417" s="14"/>
+      <c r="C417" s="14"/>
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+      <c r="F417" s="14"/>
+      <c r="G417" s="14"/>
+      <c r="H417" s="14"/>
+      <c r="I417" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J417" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K417" s="16"/>
+      <c r="L417" s="16"/>
+      <c r="M417" s="16"/>
+      <c r="N417" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10365,21 +11173,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J417">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K417" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L417" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M417" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E8E893-79D6-4C52-B726-6346D27A8054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE86F14-6E20-406E-BFD3-E30432EB672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -491,11 +491,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,74 +979,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>54</v>
       </c>
       <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="20">
         <v>12602993</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>55</v>
       </c>
       <c r="C3" s="21"/>
-      <c r="D3" s="20"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1118,7 +1118,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I85" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
@@ -3025,26 +3025,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="14">
+        <v>450</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>20</v>
+      </c>
+      <c r="F48" s="14">
+        <v>60</v>
+      </c>
+      <c r="G48" s="14">
+        <v>1</v>
+      </c>
+      <c r="H48" s="14">
+        <v>60</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
@@ -4200,7 +4224,7 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" ref="I86:I149" si="5">IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
+        <f t="shared" ref="I101:I149" si="5">IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
         <v/>
       </c>
       <c r="J101" s="15" t="str">

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE86F14-6E20-406E-BFD3-E30432EB672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9450B7F8-0D4F-4AF2-ADBF-BE1781180509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,6 +355,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -450,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -496,6 +502,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3071,95 +3080,171 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>80</v>
+      </c>
+      <c r="E49" s="14">
+        <v>20</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>40</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
+        <v>860</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B50" s="14">
+        <v>500</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>40</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>30</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
+        <v>850</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B51" s="14">
+        <v>460</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>0</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
+        <v>980</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="23">
+        <v>46295</v>
+      </c>
+      <c r="B52" s="14">
+        <v>520</v>
+      </c>
+      <c r="C52" s="14">
+        <v>0</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>0</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
+        <v>920</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13">
+        <v>46296</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9450B7F8-0D4F-4AF2-ADBF-BE1781180509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397DEABA-5F93-4228-B0F4-1FD118BD1A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,9 @@
   <si>
     <t>Well spent day.</t>
   </si>
+  <si>
+    <t>Travelled</t>
+  </si>
 </sst>
 </file>
 
@@ -497,14 +500,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -988,74 +991,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12602993</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -3118,8 +3121,12 @@
       <c r="L49" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+      <c r="M49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13">
@@ -3157,9 +3164,15 @@
       <c r="K50" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+      <c r="L50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13">
@@ -3197,12 +3210,18 @@
       <c r="K51" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="23">
+      <c r="A52" s="18">
         <v>46295</v>
       </c>
       <c r="B52" s="14">
@@ -3237,9 +3256,15 @@
       <c r="K52" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13">

--- a/12602993.xlsx
+++ b/12602993.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397DEABA-5F93-4228-B0F4-1FD118BD1A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E842C45E-C090-4319-B71B-CF9C45CEDAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Travelled</t>
+  </si>
+  <si>
+    <t>Study and spent time in home</t>
   </si>
 </sst>
 </file>
@@ -3270,91 +3273,185 @@
       <c r="A53" s="13">
         <v>46296</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="B53" s="14">
+        <v>600</v>
+      </c>
+      <c r="C53" s="14">
+        <v>10</v>
+      </c>
+      <c r="D53" s="14">
+        <v>50</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>20</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B54" s="14">
+        <v>620</v>
+      </c>
+      <c r="C54" s="14">
+        <v>20</v>
+      </c>
+      <c r="D54" s="14">
+        <v>70</v>
+      </c>
+      <c r="E54" s="14">
+        <v>10</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>30</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B55" s="14">
+        <v>540</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14">
+        <v>20</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>15</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>635</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>805</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B56" s="14">
+        <v>580</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>30</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>40</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
